--- a/results/02_taxa_assemblage/LDA_Method/ModelCompar/tables/model_summary.xlsx
+++ b/results/02_taxa_assemblage/LDA_Method/ModelCompar/tables/model_summary.xlsx
@@ -507,37 +507,37 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6571428571428571</v>
+        <v>0.92</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4885714285714285</v>
+        <v>0.7839999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1716427233814353</v>
+        <v>0.1736202753136857</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6304412021272753</v>
+        <v>0.9306250264266624</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1513058455470651</v>
+        <v>0.111421147334994</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3869972325214469</v>
+        <v>0.8612500528533248</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2526496408976993</v>
+        <v>0.2228422946699881</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5617595503939196</v>
+        <v>0.9235193087696061</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2836176381540864</v>
+        <v>0.8470386175392121</v>
       </c>
       <c r="M2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -552,37 +552,37 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4733333333333334</v>
+        <v>0.6888888888888889</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1614899759913259</v>
+        <v>0.1092736964723933</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5946858944893948</v>
+        <v>0.769457529953697</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1420668996865593</v>
+        <v>0.1416423599654115</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2983963160342464</v>
+        <v>0.5558941079563785</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2428883854422913</v>
+        <v>0.2729506038866458</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5181184880071391</v>
+        <v>0.7509182752627235</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2243064292322223</v>
+        <v>0.5045045621428438</v>
       </c>
       <c r="M3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -597,37 +597,37 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.6875</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4066666666666666</v>
+        <v>0.6246666666666667</v>
       </c>
       <c r="F4" t="n">
-        <v>0.136282205390773</v>
+        <v>0.1248068136791447</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5989501730588521</v>
+        <v>0.7469901916444925</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1632843076982819</v>
+        <v>0.1748317422060473</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3037178436794551</v>
+        <v>0.5493832370876076</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2749758290581008</v>
+        <v>0.3015906437588348</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5423347223826565</v>
+        <v>0.7125387410252696</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2387925940621</v>
+        <v>0.4911720942257614</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -645,25 +645,25 @@
         <v>50</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4699999999999999</v>
+        <v>0.6739999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1252996408614167</v>
+        <v>0.1128007092176286</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5932847187759152</v>
+        <v>0.763355346233717</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1352129590339572</v>
+        <v>0.1484020709648005</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2979975412090712</v>
+        <v>0.5429612648802662</v>
       </c>
       <c r="J5" t="n">
-        <v>0.221054453615558</v>
+        <v>0.2879031206435728</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
